--- a/artfynd/A 60333-2024 artfynd.xlsx
+++ b/artfynd/A 60333-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1219712</v>
+        <v>1184644</v>
       </c>
       <c r="B2" t="n">
-        <v>86160</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4394</v>
+        <v>4392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462859.7598093322</v>
+        <v>462860</v>
       </c>
       <c r="R2" t="n">
-        <v>6933331.173587678</v>
+        <v>6933331</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +739,9 @@
           <t>2000-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1184644</v>
+        <v>1219712</v>
       </c>
       <c r="B3" t="n">
-        <v>86313</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,19 +789,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4392</v>
+        <v>4394</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462859.7598093322</v>
+        <v>462860</v>
       </c>
       <c r="R3" t="n">
-        <v>6933331.173587678</v>
+        <v>6933331</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -866,19 +846,9 @@
           <t>2000-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2000-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 60333-2024 artfynd.xlsx
+++ b/artfynd/A 60333-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1184644</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,8 +892,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1219712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>